--- a/Testes/reescala/Teste populacao e gerações/Teste1/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste1/3_melhor_escala.xlsx
@@ -3514,8 +3514,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>1</v>
+      <c r="Q27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -4513,8 +4513,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
